--- a/forms/trg/Formulir_TRG_eiarg.xlsx
+++ b/forms/trg/Formulir_TRG_eiarg.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Anwar Daud, S.KM., M.Kes.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -1121,7 +1125,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1150,7 +1154,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
